--- a/source-data/Enerium_Враги.xlsx
+++ b/source-data/Enerium_Враги.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Эхо" sheetId="6" r:id="rId6"/>
     <sheet name="Способности Эхо" sheetId="7" r:id="rId7"/>
     <sheet name="Способности биомов" sheetId="8" r:id="rId8"/>
-    <sheet name="Крафтовые боссы" sheetId="9" r:id="rId9"/>
+    <sheet name="Призванные враги" sheetId="9" r:id="rId9"/>
     <sheet name="Клан" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
@@ -22,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Биомы 2–4'!$A$1:$K$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Биомы 5–12 черновик'!$A$1:$H$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Эхо'!$A$1:$J$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Способности Эхо'!$A$1:$H$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Способности Эхо'!$A$1:$H$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Способности биомов'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Крафтовые боссы'!$A$1:$J$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Призванные враги'!$A$1:$K$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Клан'!$A$1:$H$57</definedName>
   </definedNames>
 </workbook>
@@ -135,7 +135,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Враги: биомы, Мастерская форм, Эхо, крафтовые боссы, клан</t>
+          <t xml:space="preserve">Враги: биомы, Мастерская форм, Эхо, призванные враги, клан</t>
         </is>
       </c>
       <c r="B1" s="1"/>
@@ -148,7 +148,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Все враги игры: двенадцать биомов спуска, Мастерская форм, биомы 2–4 (данные), биомы 5–12 (черновик врагов), Эхо девяти недель с Убер-боссами и Многоликим, крафтовые боссы руин и городов, пробуждённые, эхо боссов биомов, сонмы кланового босса.</t>
+          <t xml:space="preserve">Все враги игры: двенадцать биомов спуска, Мастерская форм, биомы 2–4 (данные), биомы 5–12 (черновик врагов), Эхо девяти недель с Убер-боссами и Многоликим, призванные враги — боссы руин и городов, пробуждённые, эхо боссов биомов — с типом по силе, сонмы кланового босса.</t>
         </is>
       </c>
     </row>
@@ -202,7 +202,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">a11e191d5c22ba3e — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">27ef13e424081b3a — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -299,7 +299,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">45 строк.</t>
+          <t xml:space="preserve">51 строка.</t>
         </is>
       </c>
     </row>
@@ -318,7 +318,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лист «Крафтовые боссы»</t>
+          <t xml:space="preserve">Лист «Призванные враги»</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вычеркнутая ночь (Истечение); Удар заранее (Обрыв нити)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каменный молот (Гнев недр); Затянутый узел (Удар маятника)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обсидиановые зубья (Гнев недр); Стрела, что находит цель (Кровавый смерч)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Укус отставшего (Порезы); Туда, где слабее (Погребальный костёр)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горсть искр (Искра); Низкий полёт (Огненный вал)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Три укола (Гнев недр); Снова у входа (Застывание)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Три пасти (Искра); Смена маски (Пыльный вихрь)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Серп на длинной рукояти (Погребальный костёр); Пелена (Удар маятника)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">элита</t>
+          <t xml:space="preserve">forgotten</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удар из тени (Кровавый смерч); Тень камня (Удар маятника)</t>
+          <t xml:space="preserve">Эхо.Многоликий.act1; Эхо.Многоликий.act2; Эхо.Многоликий.pas; Эхо.Многоликий.react; Эхо.Многоликий.ult1 · ульта; Эхо.Многоликий.ult2 · ульта</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -19127,8 +19127,220 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо.Многоликий.act1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">many</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чужое лицо</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Без школы</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">активная</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Надевает лицо героя: удар на 260 % — и забирает себе все его баффы и щит.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">steal</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо.Многоликий.act2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">many</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Возвращённое лицо</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Без школы</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">активная</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Снова надевает лицо павшего защитника: тот встаёт с 40 % здоровья. Каждый встаёт раз за бой.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">revive</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо.Многоликий.pas</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">many</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Венец масок</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Без школы</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">пассивка</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лица недели держат венец: −8 % получаемого урона за каждого живого защитника и +12 % к урону за каждого павшего.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guardPerAlly</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо.Многоликий.react</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">many</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Смена лица</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Без школы</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">активная</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Когда за атаку с него сорвана половина здоровья, он сразу меняет лицо — применяет «Новое лицо».</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cast</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо.Многоликий.ult1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">many</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тысяча лиц</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Без школы</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ульта</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Венец раскрывается: по 140 % всему отряду, и в ужасе перед тысячей лиц герои пропускают ход — до первого удара по ним.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Эхо.Многоликий.ult2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">many</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое лицо</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Без школы</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ульта</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сбрасывает изувеченное лицо и надевает свежее: лечит себя на 200 % главной силы и снимает два вредных эффекта.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H46"/>
+  <autoFilter ref="A1:H52"/>
 </worksheet>
 </file>
 
@@ -19634,19 +19846,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="70" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="70" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19657,45 +19870,50 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вид</t>
+          <t xml:space="preserve">Вид призыва</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Тип по силе</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Цикл</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Место</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Враг</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Титул</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Раса</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Ремесло</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Лор</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Для команды</t>
         </is>
@@ -19709,40 +19927,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">I</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">Заброшенная дорога</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">Хатт-Уру</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">ловчий станции</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытый. Кормил тех, кто строил станцию: ходил за зверем по дороге, которой ещё не было. Народа, строившего дорогу, давно нет.</t>
         </is>
@@ -19761,30 +19984,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Заброшенная дорога</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">Хатт-Уру, ловчий станции · пробуждённый</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит и строителей, и зверя, и дорогу, которой ещё не было.</t>
         </is>
@@ -19798,35 +20026,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t xml:space="preserve">I</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Старый подкоп</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">Бур у стены</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Машина прежнего народа: ею пробивались вниз, пока хозяева не уснули у стены. Встала вместе с ними и больше не заводилась.</t>
         </is>
@@ -19845,30 +20078,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">Старый подкоп</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">Бур у стены · пробуждённый</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит, куда шёл, и снова идёт.</t>
         </is>
@@ -19882,40 +20120,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · город</t>
+          <t xml:space="preserve">босс города</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Убер</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t xml:space="preserve">I</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">Кромка Алаэля</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">Торбьёрн</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">ярл, пришедший за дровами</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Северный ярл, что привёл десант к южной кромке Алаэля за древесиной. Лес поглотил его вместе с ладьями; север с тех пор покупает дрова по портам.</t>
         </is>
@@ -19934,30 +20177,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">Кромка Алаэля</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">Торбьёрн, ярл, пришедший за дровами · пробуждённый</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит и море, и лес, который пророс сквозь его шлем.</t>
         </is>
@@ -19971,40 +20219,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Засыпанная башня</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">Лу-Ниэт</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">книжница башни</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытая. Хранила знание своего народа и сама засыпала башню, чтобы его не унесли. Народа больше нет; знание осталось под землёй.</t>
         </is>
@@ -20023,30 +20276,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">Засыпанная башня</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">Лу-Ниэт, книжница башни · пробуждённая</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулась целиком: книга при ней, все страницы.</t>
         </is>
@@ -20060,40 +20318,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Сложившаяся выработка</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">Хродмар Гудок</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">что считал смены под завалом</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">Дворфы</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Бригадир дворфской смены. Когда тряхнуло, он остался внизу со своими и считал смены по гудку, пока было кому дуть. Эхо помнит его за этим счётом.</t>
         </is>
@@ -20112,30 +20375,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">Сложившаяся выработка</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">Хродмар Гудок, что считал смены под завалом · пробуждённый</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">Дворфы</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит каждую смену и каждого, кто стоял рядом.</t>
         </is>
@@ -20149,35 +20417,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Источенное хранилище</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">Матка каменных жуков</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Матка каменных жуков, выросшая на чужом знании. Она источила хранилище до пыли и не отдаёт того, что осталось.</t>
         </is>
@@ -20196,30 +20469,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">Источенное хранилище</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">Матка каменных жуков · пробуждённая</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулась целиком: помнит каждую плиту, которую источила, и что на ней было.</t>
         </is>
@@ -20233,40 +20511,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · город</t>
+          <t xml:space="preserve">босс города</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Убер</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ярусы над пустотой</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t xml:space="preserve">Огнемётный привод</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">у узких ворот</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Машина обороны у узких ворот Стоун-Хейма: огнемётный привод на станине. Её завели однажды, и она не помнит, как останавливаться.</t>
         </is>
@@ -20285,30 +20568,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ярусы над пустотой</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">Огнемётный привод, у узких ворот · пробуждённый</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит каждый день у ворот и каждого, кого не пустил.</t>
         </is>
@@ -20322,35 +20610,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">Поле древней битвы</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">Зверь без всадника</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Боевой зверь прежнего войска в кованом налобнике. Всадник пал первым, зверь — последним; поле он так и не отдал.</t>
         </is>
@@ -20369,30 +20662,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">Поле древней битвы</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">Зверь без всадника · пробуждённый</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит всадника и снова ждёт его в бою.</t>
         </is>
@@ -20406,35 +20704,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve">Курган клинков</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">Пламя над курганом</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">Саганы</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Саган огня, заметивший себя в погребальном костре. Он горит над курганом с той ночи и не даёт никому забрать оружие мёртвых.</t>
         </is>
@@ -20453,30 +20756,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t xml:space="preserve">Курган клинков</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">Пламя над курганом · пробуждённое</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">Саганы</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулось целиком: помнит каждого, кого укрыло, и каждого, кто пытался забрать.</t>
         </is>
@@ -20490,35 +20798,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">Выжженная крепость</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t xml:space="preserve">Таран у ворот</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Осадная машина прежнего войска. Её сожгли вместе с крепостью, но она дошла до ворот и там осталась. Качается до сих пор.</t>
         </is>
@@ -20537,30 +20850,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">Выжженная крепость</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">Таран у ворот · пробуждённый</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит каждый удар и каждую ночь осады.</t>
         </is>
@@ -20574,35 +20892,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Горн на склоне</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнец для тех, кто не придёт</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытый. Ковал оружие для своего народа на склоне огненной горы. Народа нет, гора остыла, а он куёт до сих пор — для тех, кто не придёт.</t>
         </is>
@@ -20621,30 +20944,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">Горн на склоне</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнец для тех, кто не придёт · пробуждённый</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит свой народ и каждого, для кого ковал.</t>
         </is>
@@ -20658,40 +20986,45 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · город</t>
+          <t xml:space="preserve">босс города</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Убер</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Песок Сеймура</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Сеймур</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">учитель</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Вождь севера и лучший боец своего времени, учитель того, кто его превзошёл. Песок Арены назван его именем. Эхо помнит его на этом песке.</t>
         </is>
@@ -20710,30 +21043,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">Песок Сеймура</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Сеймур, учитель · пробуждённый</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит каждого ученика и последний бой.</t>
         </is>
@@ -20747,40 +21085,45 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">Затопленное святилище</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Меда-Ус</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">хранительница воды</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытая. Держала воду святилища чистой, пока его не затопило; вода осталась чистой и после. Её народа давно нет.</t>
         </is>
@@ -20799,30 +21142,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">Затопленное святилище</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t xml:space="preserve">Меда-Ус, хранительница воды · пробуждённая</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулась целиком: святилище при ней, и вода в нём чиста.</t>
         </is>
@@ -20836,35 +21184,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t xml:space="preserve">Маяк на мели</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t xml:space="preserve">Спящий под маяком</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Морской зверь, что жил под маяком и кормился его светом. Свет погас, море ушло, а он остался спать на мели.</t>
         </is>
@@ -20883,30 +21236,35 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">Маяк на мели</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t xml:space="preserve">Спящий под маяком · пробуждённый</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит свет, море и тех, кто ходил мимо.</t>
         </is>
@@ -20920,35 +21278,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">Площадь жребия</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t xml:space="preserve">Жребиемёт</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Машина, которую народ площади построил, чтобы жребий не зависел от руки. Она бросает кости до сих пор — и всегда выпадает «ещё раз».</t>
         </is>
@@ -20967,30 +21330,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">Площадь жребия</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t xml:space="preserve">Жребиемёт · пробуждённый</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит каждый бросок и каждого, кого осудил жребий.</t>
         </is>
@@ -21004,35 +21372,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">Шлюз без реки</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t xml:space="preserve">Смотритель шлюза</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Смотритель шлюза прежнего народа. Река ушла, а он поднимает и опускает затворы по часам, как поднимал корабли.</t>
         </is>
@@ -21051,30 +21424,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t xml:space="preserve">Шлюз без реки</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t xml:space="preserve">Смотритель шлюза · пробуждённый</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит все воды и все корабли.</t>
         </is>
@@ -21088,35 +21466,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · город</t>
+          <t xml:space="preserve">босс города</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Убер</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ступени падающей реки</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t xml:space="preserve">Страж арки</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">Саганы</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Саган воды, связанный синим камнем в замке арки. Он держит воду чистой, мост целым и гавань спокойной — и не пускает к воде тех, кто её мутит.</t>
         </is>
@@ -21135,30 +21518,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ступени падающей реки</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t xml:space="preserve">Страж арки · пробуждённый</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">Саганы</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: держит все арки города, а не одну.</t>
         </is>
@@ -21172,40 +21560,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t xml:space="preserve">Штольня искателей</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ведда-Ор</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">что спускала на верёвке</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">Портняжное дело</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытая. Её народ копал к середине мира задолго до Эндалора. Она спускала своих на верёвке и слушала свист снизу, пока свистеть не стало некому.</t>
         </is>
@@ -21224,30 +21617,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">Штольня искателей</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ведда-Ор, что спускала на верёвке · пробуждённая</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">Забытые</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">Портняжное дело</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулась целиком: помнит каждый узел и каждого, кого спускала.</t>
         </is>
@@ -21261,35 +21659,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">Солнечный круг</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t xml:space="preserve">Тень полудня</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">Саганы</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Саган, заметивший себя в тени столба. Тень стоит на одном часе, и он стоит вместе с ней.</t>
         </is>
@@ -21308,30 +21711,35 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t xml:space="preserve">Солнечный круг</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t xml:space="preserve">Тень полудня · пробуждённая</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">Саганы</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулась целиком: помнит каждый час круга, а не один.</t>
         </is>
@@ -21345,35 +21753,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">Опоздавший караван</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t xml:space="preserve">Погонщик, что опоздал</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Погонщик каравана золотого века. Он опаздывает на один день уже триста лет и всё ещё надеется успеть.</t>
         </is>
@@ -21392,30 +21805,35 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t xml:space="preserve">Опоздавший караван</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t xml:space="preserve">Погонщик, что опоздал · пробуждённый</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит весь путь и тех, кто ждал.</t>
         </is>
@@ -21429,35 +21847,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">Дом с остановленными часами</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t xml:space="preserve">Та, что ждёт</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">Эльфы</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эльфийка, что остановила все часы в доме в день, когда хозяин не вернулся. Для неё двести лет — не срок; для дома — срок.</t>
         </is>
@@ -21476,30 +21899,35 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t xml:space="preserve">Дом с остановленными часами</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t xml:space="preserve">Та, что ждёт · пробуждённая</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">Эльфы</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулась целиком: помнит, кого ждёт, и почему остановила часы.</t>
         </is>
@@ -21513,35 +21941,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t xml:space="preserve">Застывшая охота</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t xml:space="preserve">Зверь в прыжке</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Зверь, застывший в прыжке над охотниками. Стрела висит у его бока сто лет; он всё ещё прыгает.</t>
         </is>
@@ -21560,30 +21993,35 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t xml:space="preserve">Застывшая охота</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t xml:space="preserve">Зверь в прыжке · пробуждённый</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит охоту от первого следа.</t>
         </is>
@@ -21597,40 +22035,45 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · город</t>
+          <t xml:space="preserve">босс города</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Убер</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t xml:space="preserve">Довод</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t xml:space="preserve">Селестина</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">первая в архиве Доводов</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Маг, чьё имя стоит первым в архиве Доводов за века. Она вызывала всех и проигрывала вслух, пока не перестала проигрывать.</t>
         </is>
@@ -21649,30 +22092,35 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t xml:space="preserve">Довод</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t xml:space="preserve">Селестина, первая в архиве Доводов · пробуждённая</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулась целиком: помнит каждый Довод и каждого, кто признал вслух.</t>
         </is>
@@ -21686,40 +22134,45 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t xml:space="preserve">Застывший лагерь</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t xml:space="preserve">Несостоявшаяся отливка</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve">Перворождённые</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Литейную стерегли отливки, из которых боги не вышли. Культ одолел их по дороге к стене; Эхо помнит последнюю.</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -21738,35 +22191,40 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t xml:space="preserve">Застывший лагерь</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t xml:space="preserve">Несостоявшаяся отливка · пробуждённая</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">Перворождённые</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулась целиком: у отливки есть лицо, и не одно.</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -21780,40 +22238,45 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ниши глубоких залов</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t xml:space="preserve">Стоящий лицом к работе</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve">Нежить</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Дворф из ниши, что шагнул на свет, простояв сто лет. Лицо у него спокойное. Это хуже всего.</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -21832,35 +22295,40 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ниши глубоких залов</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t xml:space="preserve">Стоящий лицом к работе · пробуждённый</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">Нежить</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит цех, смену и тех, кто стоит рядом.</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -21874,40 +22342,45 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · руина</t>
+          <t xml:space="preserve">босс руины</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t xml:space="preserve">Стоянка учителей</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t xml:space="preserve">Учитель у Оболочки</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve">Искажённые</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Учитель школы Времени, что держался Энериумом в перчатке, пока перчатка не стала частью руки. Он всё ещё учит — тех, кого нет.</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -21926,35 +22399,40 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve">Стоянка учителей</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t xml:space="preserve">Учитель у Оболочки · пробуждённый</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve">Искажённые</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит, кого учил и за кем шёл вниз.</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -21968,40 +22446,45 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">крафтовый босс · город</t>
+          <t xml:space="preserve">босс города</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Убер</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t xml:space="preserve">Перекрёсток до взлёта</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t xml:space="preserve">Первый из поднявшихся</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve">Искажённые</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Черновик, что первым поднялся из середины мира к стенам города на перекрёстке. Кем он должен был стать, не знает никто — и он тоже.</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -22020,35 +22503,40 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Забытый</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">Перекрёсток до взлёта</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t xml:space="preserve">Первый из поднявшихся · пробуждённый</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve">Искажённые</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Проснулся целиком: помнит, откуда поднялся, и почему.</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -22067,30 +22555,35 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t xml:space="preserve">I</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t xml:space="preserve">Мастерская форм</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t xml:space="preserve">Первый набросок · эхо</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve">Саганы</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">Зачарование</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо первой брошенной попытки. Оно помнит, чем доделывало себя, и просит своё назад.</t>
         </is>
@@ -22109,30 +22602,35 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t xml:space="preserve">I</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t xml:space="preserve">Подземный лес</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t xml:space="preserve">Матерь стаи · эхо</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">Звери</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо той, от кого идёт весь зверь леса. Она приходит на голос выводка и помнит каждого, кого у неё забрали.</t>
         </is>
@@ -22151,30 +22649,35 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t xml:space="preserve">Библиотека Улариона</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t xml:space="preserve">Смотритель · эхо</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо машины, что тысячу лет сторожит стеллажи. Она помнит, где что лежит, — и кто что взял.</t>
         </is>
@@ -22193,30 +22696,35 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t xml:space="preserve">II</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t xml:space="preserve">Искусственный Стоун-Хейм</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t xml:space="preserve">Глава города · эхо</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t xml:space="preserve">Дворфы</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо главы города-наброска. Он не сильнее других, но за ним встаёт весь квартал — и в Эхо тоже.</t>
         </is>
@@ -22235,30 +22743,35 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузня</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнец · эхо</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо того, кто менял оружие прямо в бою. Горн у него за спиной не гас ни разу.</t>
         </is>
@@ -22277,30 +22790,35 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t xml:space="preserve">III</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t xml:space="preserve">Арена, где бой не кончался</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t xml:space="preserve">Воплощение Крога · эхо</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо той части силы Крога, что поставлена на песок при Схождении. Бой с ним не кончается: раны затягиваются раньше, чем ты замахнёшься.</t>
         </is>
@@ -22319,30 +22837,35 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t xml:space="preserve">Залы у водопадов</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t xml:space="preserve">Палач · эхо</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо стража в закрытом шлеме без прорезей. Колокол у его пояса без языка; звона он не ждёт.</t>
         </is>
@@ -22361,30 +22884,35 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t xml:space="preserve">IV</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t xml:space="preserve">Город суда</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t xml:space="preserve">Судья с весами · эхо</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузнечество</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо исполина в мантии с синей лентой. Бьёт редко и страшно; чем больше вас на него одного, тем тяжелее приговор.</t>
         </is>
@@ -22403,30 +22931,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t xml:space="preserve">Зал часов</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t xml:space="preserve">Тот, кто не дошёл · эхо</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t xml:space="preserve">Люди</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">Портняжное дело</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо искателя в изношенном плаще неведомого века. До врат ему остался шаг; раненым он не падает.</t>
         </is>
@@ -22445,30 +22978,35 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t xml:space="preserve">Лабиринт у воронки</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t xml:space="preserve">Архитектор · эхо</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t xml:space="preserve">Аппараты</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">Инженерия</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо огромного аппарата с руками-кранами. Каждый его шаг переставляет стены; он не гонится — он отрезает.</t>
         </is>
@@ -22487,35 +23025,40 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t xml:space="preserve">Литейная богов</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t xml:space="preserve">Правая рука Иридис · эхо</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t xml:space="preserve">Искажённые</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">Алхимия</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо правой руки главы культа. Свет и тьма в двух ударах; погребальная формула в чужих устах.</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
@@ -22534,41 +23077,46 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t xml:space="preserve">босс</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t xml:space="preserve">VI</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t xml:space="preserve">Сердцевина</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t xml:space="preserve">Хранитель · эхо</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t xml:space="preserve">Перворождённые</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">Охота</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Эхо последнего черновика перед Иридис. Он держит засов и не узнаёт тех, кто пришёл.</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t xml:space="preserve">да</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J67"/>
+  <autoFilter ref="A1:K67"/>
 </worksheet>
 </file>
--- a/source-data/Enerium_Враги.xlsx
+++ b/source-data/Enerium_Враги.xlsx
@@ -202,7 +202,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">27ef13e424081b3a — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">0c5b34e0458c2dd7 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Возвращённое лицо</t>
+          <t xml:space="preserve">Посмертная маска</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19192,12 +19192,12 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Снова надевает лицо павшего защитника: тот встаёт с 40 % здоровья. Каждый встаёт раз за бой.</t>
+          <t xml:space="preserve">Надевает на самого опасного героя посмертную маску: через 2 раунда она бьёт его на 320 %. Снять маску — спастись.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">revive</t>
+          <t xml:space="preserve">doom</t>
         </is>
       </c>
     </row>
@@ -19229,12 +19229,12 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лица недели держат венец: −8 % получаемого урона за каждого живого защитника и +12 % к урону за каждого павшего.</t>
+          <t xml:space="preserve">Венец поворачивается: каждый третий свой ход Многоликий сразу надевает «Чужое лицо» ещё раз. Кто сбросил или оглушил его, тот сбил венцу счёт.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">guardPerAlly</t>
+          <t xml:space="preserve">everyN</t>
         </is>
       </c>
     </row>

--- a/source-data/Enerium_Враги.xlsx
+++ b/source-data/Enerium_Враги.xlsx
@@ -190,7 +190,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-06 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -202,7 +202,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0c5b34e0458c2dd7 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">c8c7880958251f9f — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -17437,7 +17437,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ночь называет имя того, кто готов ходить первым: через 2 раунда на него падает удар — 400 %. Снять метку — спастись.</t>
+          <t xml:space="preserve">Ночь называет имя того, кто готов ходить первым: через 2 раунда на него падает удар — 400 %. Снять с героя это имя — спастись.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Когда Узел бьют, 20 % шанс завязать на ударившем узелок — стак старения. Урон по времени узелков не завязывает.</t>
+          <t xml:space="preserve">Когда Узел бьют, 20 % шанс завязать на ударившем узелок — стак старения: урон каждый ход, с каждым ходом сильнее. Урон по времени узелков не завязывает.</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">На ободе все дни, кроме одного: остановка ложится на колесо всегда — иммунитет по рангу её не режет.</t>
+          <t xml:space="preserve">На ободе все дни, кроме одного: остановка — ход последним, без ульты — ложится на колесо всегда: иммунитет по рангу её не режет.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Когда здоровье колеса падает ниже половины — раз за бой, — оно сразу применяет «Новый круг». Под остановкой счёт не начинается.</t>
+          <t xml:space="preserve">Когда здоровье колеса падает ниже половины — раз за бой, — оно сразу применяет «Новый круг». Под остановкой (ход последним, без ульты) счёт не начинается.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Олень бьёт рогами трёх героев — по 100 %; золото высекает огонь: каждому — стак горения.</t>
+          <t xml:space="preserve">Олень бьёт рогами трёх героев — по 100 %; золото высекает огонь: каждому — стак горения, урон каждый ход.</t>
         </is>
       </c>
     </row>
@@ -18217,7 +18217,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зеркала возвращают атакующему четверть урона от каждого удара по Солнцу. Разбитое зеркало не отражает: под осыпанием отражения нет.</t>
+          <t xml:space="preserve">Зеркала возвращают атакующему четверть урона от каждого удара по Солнцу. Разбитое зеркало не отражает: под осыпанием (меньше физической защиты) отражения нет.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Солнца падают на отряд: каждому сразу 3 стака горения, по 45 % за ход, 3 раунда.</t>
+          <t xml:space="preserve">Солнца падают на отряд: каждому сразу 3 стака горения — урон по 45 % каждый ход, 3 раунда.</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пятое горит ярче всех: урон по всему отряду, по 150 %; на ком горение, у того оно вспыхивает заново с двойной силой.</t>
+          <t xml:space="preserve">Пятое горит ярче всех: урон по всему отряду, по 150 %; на ком горение (урон каждый ход), у того оно вспыхивает заново с двойной силой.</t>
         </is>
       </c>
     </row>
@@ -18407,7 +18407,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Медная кожа: удары по стражу на 40 % слабее. Жила в пяте закрыта гвоздём — пока на страже метка, кожа не держит.</t>
+          <t xml:space="preserve">Медная кожа: удары по стражу на 40 % слабее. Жила в пяте закрыта гвоздём — пока на страже метка (больше получаемого урона), кожа не держит.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раскалённая медь проходит по всему отряду: по 100 % и стак горения каждому.</t>
+          <t xml:space="preserve">Раскалённая медь проходит по всему отряду: по 100 % и стак горения каждому — урон каждый ход.</t>
         </is>
       </c>
     </row>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Страж забивает гвоздь в пяту: лечит себя на 150 % и снимает с себя два дебаффа — метку тоже.</t>
+          <t xml:space="preserve">Страж забивает гвоздь в пяту: лечит себя на 150 % и снимает с себя два дебаффа — метку (больше получаемого урона) тоже.</t>
         </is>
       </c>
     </row>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Царь поднимает павшего защитника с 40 % здоровья. Сгоревший не встаёт: на ком в миг гибели было горение, того не поднять.</t>
+          <t xml:space="preserve">Царь поднимает павшего защитника с 40 % здоровья. Сгоревший не встаёт: на ком в миг гибели было горение (урон каждый ход), того не поднять.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
